--- a/backend/data/excel/dbaed2656211_data.xlsx
+++ b/backend/data/excel/dbaed2656211_data.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-23 09:48:10</t>
+          <t>2025-09-25 06:21:36</t>
         </is>
       </c>
     </row>
